--- a/Mikhail_2018_2019_5x5.xlsx
+++ b/Mikhail_2018_2019_5x5.xlsx
@@ -7,16 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2018-2019 ПРЕМЬЕР-ЛИГА 5×5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2018-2019 ВЫСШАЯ ЛИГА 5×5" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2018-2019 ПРЕМЬЕР-ЛИГА 5×5 — 2 " sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2018-2019 ВЫСШАЯ ЛИГА 5×5 — 2 К" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2018-2019 ПРЕМЬЕР-ЛИГА 5×5'!$A$17:$H$87</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2018-2019 ПРЕМЬЕР-ЛИГА 5×5'!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2018-2019 ПРЕМЬЕР-ЛИГА 5×5'!$A$1:$H$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2018-2019 ВЫСШАЯ ЛИГА 5×5'!$A$19:$H$73</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2018-2019 ВЫСШАЯ ЛИГА 5×5'!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2018-2019 ВЫСШАЯ ЛИГА 5×5'!$A$1:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2018-2019 ПРЕМЬЕР-ЛИГА 5×5 — 2 '!$A$17:$H$87</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2018-2019 ПРЕМЬЕР-ЛИГА 5×5 — 2 '!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2018-2019 ПРЕМЬЕР-ЛИГА 5×5 — 2 '!$A$1:$H$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2018-2019 ВЫСШАЯ ЛИГА 5×5 — 2 К'!$A$19:$H$127</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2018-2019 ВЫСШАЯ ЛИГА 5×5 — 2 К'!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2018-2019 ВЫСШАЯ ЛИГА 5×5 — 2 К'!$A$1:$H$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,7 +43,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="8"/>
+      <sz val="7"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -64,57 +64,32 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="000F172A"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <color rgb="00475569"/>
       <sz val="10"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="0094A3B8"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="000F172A"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="0094A3B8"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="00475569"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="0064748B"/>
       <sz val="8"/>
@@ -190,16 +165,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -216,7 +191,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,53 +203,29 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -658,21 +609,21 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2018-2019 ПРЕМЬЕР-ЛИГА 5×5</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>2018-2019 ПРЕМЬЕР-ЛИГА 5×5 — 2 КРУГА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сезон 2018-2019  •  Формат 5×5  •  ДВОЙНОЙ КРУГ (дома/в гостях)  •  Старт: 2018-09-08  •  18:00  •  Манеж 5×5  •  8 команд</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14" customHeight="1">
+          <t>Сезон 2018-2019  •  5×5  •  ДВОЙНОЙ КРУГ  •  2 круга  •  Старт: 2018-09-08  •  18:00  •  8 команд</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Всего туров: 14  •  Всего матчей: 56  •  Формула: каждый с каждым  •  Сгенерировано автоматически</t>
+          <t>Формула: каждый с каждым (ДВОЙНОЙ КРУГ)  •  Всего матчей: 56  •  Сгенерировано автоматически</t>
         </is>
       </c>
     </row>
@@ -911,9 +862,9 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2. РАСПИСАНИЕ МАТЧЕЙ — КРУГОВАЯ СИСТЕМА (каждый с каждым)</t>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>2. РАСПИСАНИЕ МАТЧЕЙ — ДВОЙНОЙ КРУГ</t>
         </is>
       </c>
     </row>
@@ -938,7 +889,7 @@
           <t>Хозяева</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -977,22 +928,22 @@
       <c r="A19" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>08.09.2018</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1002,37 +953,37 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="23" t="n">
+      <c r="A20" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>08.09.2018</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1042,12 +993,12 @@
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="G20" s="27" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H20" s="28" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1057,22 +1008,22 @@
       <c r="A21" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>08.09.2018</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1082,37 +1033,37 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="23" t="n">
+      <c r="A22" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>08.09.2018</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1122,12 +1073,12 @@
           <t>Молот</t>
         </is>
       </c>
-      <c r="G22" s="27" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1148,25 +1099,25 @@
       <c r="H23" s="16" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="23" t="n">
+      <c r="A24" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>15.09.2018</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1176,12 +1127,12 @@
           <t>68 школа</t>
         </is>
       </c>
-      <c r="G24" s="27" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1191,22 +1142,22 @@
       <c r="A25" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>15.09.2018</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1216,37 +1167,37 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="23" t="n">
+      <c r="A26" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>15.09.2018</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1256,12 +1207,12 @@
           <t>Молот</t>
         </is>
       </c>
-      <c r="G26" s="27" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1271,22 +1222,22 @@
       <c r="A27" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>15.09.2018</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1296,12 +1247,12 @@
           <t>Комета</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1325,22 +1276,22 @@
       <c r="A29" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>22.09.2018</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1350,37 +1301,37 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="23" t="n">
+      <c r="A30" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>22.09.2018</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1390,12 +1341,12 @@
           <t>Молот</t>
         </is>
       </c>
-      <c r="G30" s="27" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H30" s="28" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1405,22 +1356,22 @@
       <c r="A31" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>22.09.2018</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1430,37 +1381,37 @@
           <t>Комета</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="23" t="n">
+      <c r="A32" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>22.09.2018</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1470,12 +1421,12 @@
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="G32" s="27" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H32" s="28" t="inlineStr">
+      <c r="H32" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1496,25 +1447,25 @@
       <c r="H33" s="16" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="23" t="n">
+      <c r="A34" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>29.09.2018</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1524,12 +1475,12 @@
           <t>68 школа</t>
         </is>
       </c>
-      <c r="G34" s="27" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1539,22 +1490,22 @@
       <c r="A35" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>29.09.2018</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1564,37 +1515,37 @@
           <t>Комета</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="23" t="n">
+      <c r="A36" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>29.09.2018</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1604,12 +1555,12 @@
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="G36" s="27" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H36" s="28" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1619,22 +1570,22 @@
       <c r="A37" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>29.09.2018</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1644,12 +1595,12 @@
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1673,22 +1624,22 @@
       <c r="A39" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>06.10.2018</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1698,37 +1649,37 @@
           <t>Комета</t>
         </is>
       </c>
-      <c r="G39" s="21" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="23" t="n">
+      <c r="A40" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>06.10.2018</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1738,12 +1689,12 @@
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="G40" s="27" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H40" s="28" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1753,22 +1704,22 @@
       <c r="A41" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>06.10.2018</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1778,37 +1729,37 @@
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="G41" s="21" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="23" t="n">
+      <c r="A42" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>06.10.2018</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1818,12 +1769,12 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G42" s="27" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H42" s="28" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1844,25 +1795,25 @@
       <c r="H43" s="16" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="23" t="n">
+      <c r="A44" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>13.10.2018</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D44" s="25" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1872,12 +1823,12 @@
           <t>68 школа</t>
         </is>
       </c>
-      <c r="G44" s="27" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H44" s="28" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1887,22 +1838,22 @@
       <c r="A45" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>13.10.2018</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D45" s="19" t="inlineStr">
+      <c r="D45" s="18" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1912,37 +1863,37 @@
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="G45" s="21" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H45" s="22" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="23" t="n">
+      <c r="A46" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>13.10.2018</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D46" s="25" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1952,12 +1903,12 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G46" s="27" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H46" s="28" t="inlineStr">
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -1967,22 +1918,22 @@
       <c r="A47" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>13.10.2018</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D47" s="19" t="inlineStr">
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1992,12 +1943,12 @@
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="G47" s="21" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H47" s="22" t="inlineStr">
+      <c r="H47" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2021,22 +1972,22 @@
       <c r="A49" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>20.10.2018</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D49" s="19" t="inlineStr">
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2046,37 +1997,37 @@
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="G49" s="21" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H49" s="22" t="inlineStr">
+      <c r="H49" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="23" t="n">
+      <c r="A50" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>20.10.2018</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D50" s="25" t="inlineStr">
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2086,12 +2037,12 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G50" s="27" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H50" s="28" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2101,22 +2052,22 @@
       <c r="A51" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>20.10.2018</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D51" s="19" t="inlineStr">
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2126,37 +2077,37 @@
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="G51" s="21" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H51" s="22" t="inlineStr">
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="23" t="n">
+      <c r="A52" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B52" s="24" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>20.10.2018</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D52" s="25" t="inlineStr">
+      <c r="D52" s="20" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2166,12 +2117,12 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G52" s="27" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H52" s="28" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2192,25 +2143,25 @@
       <c r="H53" s="16" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="23" t="n">
+      <c r="A54" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>27.10.2018</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D54" s="25" t="inlineStr">
+      <c r="D54" s="20" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2220,12 +2171,12 @@
           <t>68 школа</t>
         </is>
       </c>
-      <c r="G54" s="27" t="inlineStr">
+      <c r="G54" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H54" s="28" t="inlineStr">
+      <c r="H54" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2235,22 +2186,22 @@
       <c r="A55" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>27.10.2018</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D55" s="18" t="inlineStr">
         <is>
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2260,37 +2211,37 @@
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="G55" s="21" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H55" s="22" t="inlineStr">
+      <c r="H55" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="23" t="n">
+      <c r="A56" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>27.10.2018</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="C56" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D56" s="25" t="inlineStr">
+      <c r="D56" s="20" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2300,12 +2251,12 @@
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="G56" s="27" t="inlineStr">
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H56" s="28" t="inlineStr">
+      <c r="H56" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2315,22 +2266,22 @@
       <c r="A57" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>27.10.2018</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="D57" s="18" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2340,12 +2291,12 @@
           <t>Комета</t>
         </is>
       </c>
-      <c r="G57" s="21" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H57" s="22" t="inlineStr">
+      <c r="H57" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2369,22 +2320,22 @@
       <c r="A59" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B59" s="18" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>03.11.2018</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="D59" s="18" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="E59" s="20" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2394,37 +2345,37 @@
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="G59" s="21" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H59" s="22" t="inlineStr">
+      <c r="H59" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="23" t="n">
+      <c r="A60" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B60" s="24" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>03.11.2018</t>
         </is>
       </c>
-      <c r="C60" s="24" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D60" s="25" t="inlineStr">
+      <c r="D60" s="20" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2434,12 +2385,12 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G60" s="27" t="inlineStr">
+      <c r="G60" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H60" s="28" t="inlineStr">
+      <c r="H60" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2449,22 +2400,22 @@
       <c r="A61" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>03.11.2018</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D61" s="19" t="inlineStr">
+      <c r="D61" s="18" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="E61" s="20" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2474,37 +2425,37 @@
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="G61" s="21" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H61" s="22" t="inlineStr">
+      <c r="H61" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="23" t="n">
+      <c r="A62" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B62" s="24" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>03.11.2018</t>
         </is>
       </c>
-      <c r="C62" s="24" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D62" s="25" t="inlineStr">
+      <c r="D62" s="20" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2514,12 +2465,12 @@
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="G62" s="27" t="inlineStr">
+      <c r="G62" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H62" s="28" t="inlineStr">
+      <c r="H62" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2540,25 +2491,25 @@
       <c r="H63" s="16" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="23" t="n">
+      <c r="A64" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B64" s="24" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>10.11.2018</t>
         </is>
       </c>
-      <c r="C64" s="24" t="inlineStr">
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D64" s="25" t="inlineStr">
+      <c r="D64" s="20" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2568,12 +2519,12 @@
           <t>68 школа</t>
         </is>
       </c>
-      <c r="G64" s="27" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H64" s="28" t="inlineStr">
+      <c r="H64" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2583,22 +2534,22 @@
       <c r="A65" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B65" s="18" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>10.11.2018</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D65" s="19" t="inlineStr">
+      <c r="D65" s="18" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="E65" s="20" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2608,37 +2559,37 @@
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="G65" s="21" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H65" s="22" t="inlineStr">
+      <c r="H65" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="23" t="n">
+      <c r="A66" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B66" s="24" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>10.11.2018</t>
         </is>
       </c>
-      <c r="C66" s="24" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D66" s="25" t="inlineStr">
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2648,12 +2599,12 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G66" s="27" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H66" s="28" t="inlineStr">
+      <c r="H66" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2663,22 +2614,22 @@
       <c r="A67" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B67" s="18" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>10.11.2018</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D67" s="19" t="inlineStr">
+      <c r="D67" s="18" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2688,12 +2639,12 @@
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="G67" s="21" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H67" s="22" t="inlineStr">
+      <c r="H67" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2717,22 +2668,22 @@
       <c r="A69" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B69" s="18" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>17.11.2018</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D69" s="19" t="inlineStr">
+      <c r="D69" s="18" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="E69" s="20" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2742,37 +2693,37 @@
           <t>Молот</t>
         </is>
       </c>
-      <c r="G69" s="21" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H69" s="22" t="inlineStr">
+      <c r="H69" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="23" t="n">
+      <c r="A70" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="B70" s="24" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>17.11.2018</t>
         </is>
       </c>
-      <c r="C70" s="24" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D70" s="25" t="inlineStr">
+      <c r="D70" s="20" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="E70" s="26" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2782,12 +2733,12 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G70" s="27" t="inlineStr">
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H70" s="28" t="inlineStr">
+      <c r="H70" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2797,22 +2748,22 @@
       <c r="A71" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B71" s="18" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>17.11.2018</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D71" s="19" t="inlineStr">
+      <c r="D71" s="18" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="E71" s="20" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2822,37 +2773,37 @@
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="G71" s="21" t="inlineStr">
+      <c r="G71" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H71" s="22" t="inlineStr">
+      <c r="H71" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="23" t="n">
+      <c r="A72" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="B72" s="24" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>17.11.2018</t>
         </is>
       </c>
-      <c r="C72" s="24" t="inlineStr">
+      <c r="C72" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D72" s="25" t="inlineStr">
+      <c r="D72" s="20" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="E72" s="26" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2862,12 +2813,12 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G72" s="27" t="inlineStr">
+      <c r="G72" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H72" s="28" t="inlineStr">
+      <c r="H72" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2888,25 +2839,25 @@
       <c r="H73" s="16" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="23" t="n">
+      <c r="A74" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B74" s="24" t="inlineStr">
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>24.11.2018</t>
         </is>
       </c>
-      <c r="C74" s="24" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D74" s="25" t="inlineStr">
+      <c r="D74" s="20" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="E74" s="26" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2916,12 +2867,12 @@
           <t>68 школа</t>
         </is>
       </c>
-      <c r="G74" s="27" t="inlineStr">
+      <c r="G74" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H74" s="28" t="inlineStr">
+      <c r="H74" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -2931,22 +2882,22 @@
       <c r="A75" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B75" s="18" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>24.11.2018</t>
         </is>
       </c>
-      <c r="C75" s="18" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D75" s="19" t="inlineStr">
+      <c r="D75" s="18" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="E75" s="20" t="inlineStr">
+      <c r="E75" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2956,37 +2907,37 @@
           <t>Молот</t>
         </is>
       </c>
-      <c r="G75" s="21" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H75" s="22" t="inlineStr">
+      <c r="H75" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="23" t="n">
+      <c r="A76" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B76" s="24" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>24.11.2018</t>
         </is>
       </c>
-      <c r="C76" s="24" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D76" s="25" t="inlineStr">
+      <c r="D76" s="20" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="E76" s="26" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2996,12 +2947,12 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G76" s="27" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H76" s="28" t="inlineStr">
+      <c r="H76" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -3011,22 +2962,22 @@
       <c r="A77" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B77" s="18" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>24.11.2018</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D77" s="19" t="inlineStr">
+      <c r="D77" s="18" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E77" s="20" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3036,12 +2987,12 @@
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="G77" s="21" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H77" s="22" t="inlineStr">
+      <c r="H77" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -3065,22 +3016,22 @@
       <c r="A79" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B79" s="18" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>01.12.2018</t>
         </is>
       </c>
-      <c r="C79" s="18" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D79" s="19" t="inlineStr">
+      <c r="D79" s="18" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3090,37 +3041,37 @@
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="G79" s="21" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H79" s="22" t="inlineStr">
+      <c r="H79" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="23" t="n">
+      <c r="A80" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="B80" s="24" t="inlineStr">
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>01.12.2018</t>
         </is>
       </c>
-      <c r="C80" s="24" t="inlineStr">
+      <c r="C80" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D80" s="25" t="inlineStr">
+      <c r="D80" s="20" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="E80" s="26" t="inlineStr">
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3130,12 +3081,12 @@
           <t>Комета</t>
         </is>
       </c>
-      <c r="G80" s="27" t="inlineStr">
+      <c r="G80" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H80" s="28" t="inlineStr">
+      <c r="H80" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -3145,22 +3096,22 @@
       <c r="A81" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B81" s="18" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>01.12.2018</t>
         </is>
       </c>
-      <c r="C81" s="18" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D81" s="19" t="inlineStr">
+      <c r="D81" s="18" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E81" s="20" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3170,37 +3121,37 @@
           <t>Молот</t>
         </is>
       </c>
-      <c r="G81" s="21" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H81" s="22" t="inlineStr">
+      <c r="H81" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="23" t="n">
+      <c r="A82" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="B82" s="24" t="inlineStr">
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>01.12.2018</t>
         </is>
       </c>
-      <c r="C82" s="24" t="inlineStr">
+      <c r="C82" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D82" s="25" t="inlineStr">
+      <c r="D82" s="20" t="inlineStr">
         <is>
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="E82" s="26" t="inlineStr">
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3210,12 +3161,12 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G82" s="27" t="inlineStr">
+      <c r="G82" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H82" s="28" t="inlineStr">
+      <c r="H82" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -3236,25 +3187,25 @@
       <c r="H83" s="16" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="23" t="n">
+      <c r="A84" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B84" s="24" t="inlineStr">
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>08.12.2018</t>
         </is>
       </c>
-      <c r="C84" s="24" t="inlineStr">
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D84" s="25" t="inlineStr">
+      <c r="D84" s="20" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="E84" s="26" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3264,12 +3215,12 @@
           <t>68 школа</t>
         </is>
       </c>
-      <c r="G84" s="27" t="inlineStr">
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H84" s="28" t="inlineStr">
+      <c r="H84" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -3279,22 +3230,22 @@
       <c r="A85" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B85" s="18" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>08.12.2018</t>
         </is>
       </c>
-      <c r="C85" s="18" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D85" s="19" t="inlineStr">
+      <c r="D85" s="18" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E85" s="20" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3304,37 +3255,37 @@
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="G85" s="21" t="inlineStr">
+      <c r="G85" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H85" s="22" t="inlineStr">
+      <c r="H85" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="23" t="n">
+      <c r="A86" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B86" s="24" t="inlineStr">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>08.12.2018</t>
         </is>
       </c>
-      <c r="C86" s="24" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D86" s="25" t="inlineStr">
+      <c r="D86" s="20" t="inlineStr">
         <is>
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="E86" s="26" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3344,12 +3295,12 @@
           <t>Комета</t>
         </is>
       </c>
-      <c r="G86" s="27" t="inlineStr">
+      <c r="G86" s="13" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H86" s="28" t="inlineStr">
+      <c r="H86" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -3359,22 +3310,22 @@
       <c r="A87" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B87" s="18" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>08.12.2018</t>
         </is>
       </c>
-      <c r="C87" s="18" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D87" s="19" t="inlineStr">
+      <c r="D87" s="18" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E87" s="20" t="inlineStr">
+      <c r="E87" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3384,21 +3335,21 @@
           <t>Молот</t>
         </is>
       </c>
-      <c r="G87" s="21" t="inlineStr">
+      <c r="G87" s="9" t="inlineStr">
         <is>
           <t>Манеж 5×5</t>
         </is>
       </c>
-      <c r="H87" s="22" t="inlineStr">
+      <c r="H87" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29" t="inlineStr">
-        <is>
-          <t>* Счёт вписывай в столбец «Счёт» (напр. 2:1). Для переноса матча меняй дату/время. Распечатай: Файл → Печать → Альбомная, вписать на 1 стр.</t>
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>* Счёт вписывай в столбец «Счёт» (напр. 2:1).</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3453,21 +3404,21 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2018-2019 ВЫСШАЯ ЛИГА 5×5</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>2018-2019 ВЫСШАЯ ЛИГА 5×5 — 2 КРУГА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сезон 2018-2019  •  Формат 5×5  •  ОДИН КРУГ  •  Старт: 2018-09-09  •  17:00  •  Поле 5×5 №2  •  10 команд</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14" customHeight="1">
+          <t>Сезон 2018-2019  •  5×5  •  ДВОЙНОЙ КРУГ  •  2 круга  •  Старт: 2018-09-09  •  17:00  •  10 команд</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Всего туров: 9  •  Всего матчей: 45  •  Формула: каждый с каждым  •  Сгенерировано автоматически</t>
+          <t>Формула: каждый с каждым (ДВОЙНОЙ КРУГ)  •  Всего матчей: 90  •  Сгенерировано автоматически</t>
         </is>
       </c>
     </row>
@@ -3756,9 +3707,9 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2. РАСПИСАНИЕ МАТЧЕЙ — КРУГОВАЯ СИСТЕМА (каждый с каждым)</t>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>2. РАСПИСАНИЕ МАТЧЕЙ — ДВОЙНОЙ КРУГ</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3734,7 @@
           <t>Хозяева</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3822,22 +3773,22 @@
       <c r="A21" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>09.09.2018</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3847,37 +3798,37 @@
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="23" t="n">
+      <c r="A22" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>09.09.2018</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3887,12 +3838,12 @@
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="G22" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -3902,22 +3853,22 @@
       <c r="A23" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>09.09.2018</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3927,37 +3878,37 @@
           <t>Дружба</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="23" t="n">
+      <c r="A24" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>09.09.2018</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3967,12 +3918,12 @@
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="G24" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -3982,22 +3933,22 @@
       <c r="A25" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>09.09.2018</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4007,12 +3958,12 @@
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4036,22 +3987,22 @@
       <c r="A27" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>16.09.2018</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4061,37 +4012,37 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="23" t="n">
+      <c r="A28" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>16.09.2018</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4101,12 +4052,12 @@
           <t>Дружба</t>
         </is>
       </c>
-      <c r="G28" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4116,22 +4067,22 @@
       <c r="A29" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>16.09.2018</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4141,37 +4092,37 @@
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="23" t="n">
+      <c r="A30" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>16.09.2018</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4181,12 +4132,12 @@
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="G30" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H30" s="28" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4196,22 +4147,22 @@
       <c r="A31" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>16.09.2018</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4221,12 +4172,12 @@
           <t>КС 26</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4250,22 +4201,22 @@
       <c r="A33" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>23.09.2018</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4275,37 +4226,37 @@
           <t>Дружба</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="23" t="n">
+      <c r="A34" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>23.09.2018</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4315,12 +4266,12 @@
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="G34" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4330,22 +4281,22 @@
       <c r="A35" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>23.09.2018</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4355,37 +4306,37 @@
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="23" t="n">
+      <c r="A36" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>23.09.2018</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4395,12 +4346,12 @@
           <t>КС 26</t>
         </is>
       </c>
-      <c r="G36" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H36" s="28" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4410,22 +4361,22 @@
       <c r="A37" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>23.09.2018</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4435,12 +4386,12 @@
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4464,22 +4415,22 @@
       <c r="A39" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>30.09.2018</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4489,37 +4440,37 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G39" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="23" t="n">
+      <c r="A40" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>30.09.2018</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4529,12 +4480,12 @@
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="G40" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H40" s="28" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4544,22 +4495,22 @@
       <c r="A41" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>30.09.2018</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4569,37 +4520,37 @@
           <t>КС 26</t>
         </is>
       </c>
-      <c r="G41" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="23" t="n">
+      <c r="A42" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>30.09.2018</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4609,12 +4560,12 @@
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="G42" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H42" s="28" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4624,22 +4575,22 @@
       <c r="A43" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>30.09.2018</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4649,12 +4600,12 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G43" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H43" s="22" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4678,22 +4629,22 @@
       <c r="A45" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>07.10.2018</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4703,37 +4654,37 @@
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="G45" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H45" s="22" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="23" t="n">
+      <c r="A46" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>07.10.2018</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4743,12 +4694,12 @@
           <t>КС 26</t>
         </is>
       </c>
-      <c r="G46" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H46" s="28" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4758,22 +4709,22 @@
       <c r="A47" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>07.10.2018</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4783,37 +4734,37 @@
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="G47" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H47" s="22" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="23" t="n">
+      <c r="A48" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B48" s="24" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>07.10.2018</t>
         </is>
       </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4823,12 +4774,12 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G48" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H48" s="28" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4838,22 +4789,22 @@
       <c r="A49" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>07.10.2018</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4863,12 +4814,12 @@
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="G49" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H49" s="22" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4892,22 +4843,22 @@
       <c r="A51" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>14.10.2018</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D51" s="19" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4917,37 +4868,37 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G51" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H51" s="22" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="23" t="n">
+      <c r="A52" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B52" s="24" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>14.10.2018</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D52" s="25" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4957,12 +4908,12 @@
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="G52" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H52" s="28" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -4972,22 +4923,22 @@
       <c r="A53" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>14.10.2018</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D53" s="19" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4997,37 +4948,37 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G53" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H53" s="22" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="23" t="n">
+      <c r="A54" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>14.10.2018</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5037,12 +4988,12 @@
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="G54" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H54" s="28" t="inlineStr">
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H54" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5052,22 +5003,22 @@
       <c r="A55" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>14.10.2018</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5077,12 +5028,12 @@
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="G55" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H55" s="22" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5106,22 +5057,22 @@
       <c r="A57" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>21.10.2018</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5131,37 +5082,37 @@
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="G57" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H57" s="22" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="23" t="n">
+      <c r="A58" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B58" s="24" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>21.10.2018</t>
         </is>
       </c>
-      <c r="C58" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D58" s="25" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5171,12 +5122,12 @@
           <t>Профики</t>
         </is>
       </c>
-      <c r="G58" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H58" s="28" t="inlineStr">
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5186,22 +5137,22 @@
       <c r="A59" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B59" s="18" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>21.10.2018</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="E59" s="20" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5211,37 +5162,37 @@
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="G59" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H59" s="22" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="23" t="n">
+      <c r="A60" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B60" s="24" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>21.10.2018</t>
         </is>
       </c>
-      <c r="C60" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D60" s="25" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5251,12 +5202,12 @@
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="G60" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H60" s="28" t="inlineStr">
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5266,22 +5217,22 @@
       <c r="A61" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>21.10.2018</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="E61" s="20" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5291,12 +5242,12 @@
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="G61" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H61" s="22" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5320,22 +5271,22 @@
       <c r="A63" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>28.10.2018</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E63" s="20" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5345,37 +5296,37 @@
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="G63" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H63" s="22" t="inlineStr">
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="23" t="n">
+      <c r="A64" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B64" s="24" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>28.10.2018</t>
         </is>
       </c>
-      <c r="C64" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D64" s="25" t="inlineStr">
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
         <is>
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5385,12 +5336,12 @@
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="G64" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H64" s="28" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5400,22 +5351,22 @@
       <c r="A65" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B65" s="18" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>28.10.2018</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="E65" s="20" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5425,37 +5376,37 @@
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="G65" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H65" s="22" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="23" t="n">
+      <c r="A66" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="24" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>28.10.2018</t>
         </is>
       </c>
-      <c r="C66" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D66" s="25" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5465,12 +5416,12 @@
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="G66" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H66" s="28" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H66" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5480,22 +5431,22 @@
       <c r="A67" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="18" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>28.10.2018</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D67" s="19" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5505,12 +5456,12 @@
           <t>Дружба</t>
         </is>
       </c>
-      <c r="G67" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H67" s="22" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5534,22 +5485,22 @@
       <c r="A69" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B69" s="18" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>04.11.2018</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D69" s="19" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="E69" s="20" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5559,37 +5510,37 @@
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="G69" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H69" s="22" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="23" t="n">
+      <c r="A70" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B70" s="24" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>04.11.2018</t>
         </is>
       </c>
-      <c r="C70" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D70" s="25" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="E70" s="26" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5599,12 +5550,12 @@
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="G70" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H70" s="28" t="inlineStr">
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H70" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5614,22 +5565,22 @@
       <c r="A71" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B71" s="18" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>04.11.2018</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
         <is>
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="E71" s="20" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5639,37 +5590,37 @@
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="G71" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H71" s="22" t="inlineStr">
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="23" t="n">
+      <c r="A72" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B72" s="24" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>04.11.2018</t>
         </is>
       </c>
-      <c r="C72" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D72" s="25" t="inlineStr">
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="E72" s="26" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5679,12 +5630,12 @@
           <t>Дружба</t>
         </is>
       </c>
-      <c r="G72" s="27" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H72" s="28" t="inlineStr">
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> : </t>
         </is>
@@ -5694,22 +5645,22 @@
       <c r="A73" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B73" s="18" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>04.11.2018</t>
         </is>
       </c>
-      <c r="C73" s="18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D73" s="19" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="E73" s="20" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5719,42 +5670,1977 @@
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="G73" s="21" t="inlineStr">
-        <is>
-          <t>Поле 5×5 №2</t>
-        </is>
-      </c>
-      <c r="H73" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> : </t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>* Счёт вписывай в столбец «Счёт» (напр. 2:1). Для переноса матча меняй дату/время. Распечатай: Файл → Печать → Альбомная, вписать на 1 стр.</t>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>ТУР 10  —  11.11.2018</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="n"/>
+      <c r="C74" s="16" t="n"/>
+      <c r="D74" s="16" t="n"/>
+      <c r="E74" s="16" t="n"/>
+      <c r="F74" s="16" t="n"/>
+      <c r="G74" s="16" t="n"/>
+      <c r="H74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>11.11.2018</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>11.11.2018</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>11.11.2018</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>11.11.2018</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>11.11.2018</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>ТУР 11  —  18.11.2018</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="n"/>
+      <c r="C80" s="16" t="n"/>
+      <c r="D80" s="16" t="n"/>
+      <c r="E80" s="16" t="n"/>
+      <c r="F80" s="16" t="n"/>
+      <c r="G80" s="16" t="n"/>
+      <c r="H80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>18.11.2018</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>18.11.2018</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H82" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>18.11.2018</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>18.11.2018</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="G84" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H84" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>18.11.2018</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>ТУР 12  —  25.11.2018</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="n"/>
+      <c r="C86" s="16" t="n"/>
+      <c r="D86" s="16" t="n"/>
+      <c r="E86" s="16" t="n"/>
+      <c r="F86" s="16" t="n"/>
+      <c r="G86" s="16" t="n"/>
+      <c r="H86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>25.11.2018</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>25.11.2018</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H88" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>25.11.2018</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D89" s="18" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>25.11.2018</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>25.11.2018</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>ТУР 13  —  02.12.2018</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="n"/>
+      <c r="C92" s="16" t="n"/>
+      <c r="D92" s="16" t="n"/>
+      <c r="E92" s="16" t="n"/>
+      <c r="F92" s="16" t="n"/>
+      <c r="G92" s="16" t="n"/>
+      <c r="H92" s="16" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>02.12.2018</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>02.12.2018</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>02.12.2018</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>02.12.2018</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D96" s="20" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H96" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>02.12.2018</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>ТУР 14  —  09.12.2018</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="n"/>
+      <c r="C98" s="16" t="n"/>
+      <c r="D98" s="16" t="n"/>
+      <c r="E98" s="16" t="n"/>
+      <c r="F98" s="16" t="n"/>
+      <c r="G98" s="16" t="n"/>
+      <c r="H98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>09.12.2018</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D99" s="18" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>09.12.2018</t>
+        </is>
+      </c>
+      <c r="C100" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H100" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>09.12.2018</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>09.12.2018</t>
+        </is>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="G102" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H102" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>09.12.2018</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D103" s="18" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>ТУР 15  —  16.12.2018</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="n"/>
+      <c r="C104" s="16" t="n"/>
+      <c r="D104" s="16" t="n"/>
+      <c r="E104" s="16" t="n"/>
+      <c r="F104" s="16" t="n"/>
+      <c r="G104" s="16" t="n"/>
+      <c r="H104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>16.12.2018</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D105" s="18" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>16.12.2018</t>
+        </is>
+      </c>
+      <c r="C106" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="G106" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H106" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>16.12.2018</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D107" s="18" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>16.12.2018</t>
+        </is>
+      </c>
+      <c r="C108" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="G108" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H108" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>16.12.2018</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D109" s="18" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>ТУР 16  —  23.12.2018</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="n"/>
+      <c r="C110" s="16" t="n"/>
+      <c r="D110" s="16" t="n"/>
+      <c r="E110" s="16" t="n"/>
+      <c r="F110" s="16" t="n"/>
+      <c r="G110" s="16" t="n"/>
+      <c r="H110" s="16" t="n"/>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>23.12.2018</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D111" s="18" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>23.12.2018</t>
+        </is>
+      </c>
+      <c r="C112" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H112" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>23.12.2018</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D113" s="18" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="A114" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>23.12.2018</t>
+        </is>
+      </c>
+      <c r="C114" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="G114" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H114" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>23.12.2018</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D115" s="18" t="inlineStr">
+        <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>ТУР 17  —  30.12.2018</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="n"/>
+      <c r="C116" s="16" t="n"/>
+      <c r="D116" s="16" t="n"/>
+      <c r="E116" s="16" t="n"/>
+      <c r="F116" s="16" t="n"/>
+      <c r="G116" s="16" t="n"/>
+      <c r="H116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>30.12.2018</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D117" s="18" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="A118" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>30.12.2018</t>
+        </is>
+      </c>
+      <c r="C118" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H118" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>30.12.2018</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D119" s="18" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>30.12.2018</t>
+        </is>
+      </c>
+      <c r="C120" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="G120" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H120" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>30.12.2018</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D121" s="18" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>ТУР 18  —  06.01.2019</t>
+        </is>
+      </c>
+      <c r="B122" s="16" t="n"/>
+      <c r="C122" s="16" t="n"/>
+      <c r="D122" s="16" t="n"/>
+      <c r="E122" s="16" t="n"/>
+      <c r="F122" s="16" t="n"/>
+      <c r="G122" s="16" t="n"/>
+      <c r="H122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>06.01.2019</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D123" s="18" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>06.01.2019</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D124" s="20" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="G124" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H124" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1">
+      <c r="A125" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>06.01.2019</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D125" s="18" t="inlineStr">
+        <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="15" customHeight="1">
+      <c r="A126" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>06.01.2019</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D126" s="20" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="G126" s="13" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H126" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15" customHeight="1">
+      <c r="A127" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>06.01.2019</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D127" s="18" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>Поле 5×5 №2</t>
+        </is>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> : </t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="21" t="inlineStr">
+        <is>
+          <t>* Счёт вписывай в столбец «Счёт» (напр. 2:1).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:H73"/>
-  <mergeCells count="15">
+  <autoFilter ref="A19:H127"/>
+  <mergeCells count="24">
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A98:H98"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A74:H74"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A116:H116"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A122:H122"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A32:H32"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
